--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/78.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/78.xlsx
@@ -426,13 +426,13 @@
         <v>-9.805415791441739</v>
       </c>
       <c r="E2">
-        <v>-8.416918218174226</v>
+        <v>-6.906010979411043</v>
       </c>
       <c r="F2">
-        <v>-5.64778342014505</v>
+        <v>-5.4904101809612</v>
       </c>
       <c r="G2">
-        <v>-5.175145254023231</v>
+        <v>-5.504478324269929</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-9.842162803223497</v>
       </c>
       <c r="E3">
-        <v>-7.985431629301372</v>
+        <v>-7.34554013812152</v>
       </c>
       <c r="F3">
-        <v>-5.482452055322505</v>
+        <v>-5.407125293916335</v>
       </c>
       <c r="G3">
-        <v>-4.830967697578442</v>
+        <v>-5.337318948355509</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.986668394194275</v>
       </c>
       <c r="E4">
-        <v>-8.28517585234308</v>
+        <v>-7.83682975473967</v>
       </c>
       <c r="F4">
-        <v>-5.709788376979398</v>
+        <v>-5.637093338811923</v>
       </c>
       <c r="G4">
-        <v>-4.692543856944896</v>
+        <v>-5.540828114291127</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-10.20774518125484</v>
       </c>
       <c r="E5">
-        <v>-9.350327280635241</v>
+        <v>-9.12954605886528</v>
       </c>
       <c r="F5">
-        <v>-5.585888636175274</v>
+        <v>-5.608028411749896</v>
       </c>
       <c r="G5">
-        <v>-5.185239107372469</v>
+        <v>-5.605549279583879</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-10.47258983400381</v>
       </c>
       <c r="E6">
-        <v>-11.26729825519222</v>
+        <v>-10.2576659182341</v>
       </c>
       <c r="F6">
-        <v>-5.322566377805964</v>
+        <v>-5.188657473673813</v>
       </c>
       <c r="G6">
-        <v>-6.079950455361439</v>
+        <v>-5.255382946258547</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-10.74352149094749</v>
       </c>
       <c r="E7">
-        <v>-10.8681857270002</v>
+        <v>-11.03851974832471</v>
       </c>
       <c r="F7">
-        <v>-5.093930347694078</v>
+        <v>-5.313189258806274</v>
       </c>
       <c r="G7">
-        <v>-5.43152714276655</v>
+        <v>-5.703418937361353</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-10.9923278648973</v>
       </c>
       <c r="E8">
-        <v>-13.09908410519091</v>
+        <v>-11.10074550966411</v>
       </c>
       <c r="F8">
-        <v>-5.488369083680702</v>
+        <v>-5.236202449124893</v>
       </c>
       <c r="G8">
-        <v>-6.207803724088093</v>
+        <v>-5.94912762728606</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-11.19491586506421</v>
       </c>
       <c r="E9">
-        <v>-12.68250525275131</v>
+        <v>-11.96365528877371</v>
       </c>
       <c r="F9">
-        <v>-5.20704971511817</v>
+        <v>-5.033987197325298</v>
       </c>
       <c r="G9">
-        <v>-5.25214523272114</v>
+        <v>-5.569090241559885</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-11.33590293744307</v>
       </c>
       <c r="E10">
-        <v>-13.54585882231366</v>
+        <v>-12.16151790359085</v>
       </c>
       <c r="F10">
-        <v>-5.308298577660145</v>
+        <v>-4.978512260727218</v>
       </c>
       <c r="G10">
-        <v>-5.008088505020529</v>
+        <v>-5.703001808623404</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-11.40840138377846</v>
       </c>
       <c r="E11">
-        <v>-13.45959592094155</v>
+        <v>-13.44640900463121</v>
       </c>
       <c r="F11">
-        <v>-4.68223340523753</v>
+        <v>-4.687885356026831</v>
       </c>
       <c r="G11">
-        <v>-4.959443348866478</v>
+        <v>-5.973936855557358</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-11.40680461483093</v>
       </c>
       <c r="E12">
-        <v>-14.61580137610593</v>
+        <v>-14.26717227615142</v>
       </c>
       <c r="F12">
-        <v>-4.935558097422452</v>
+        <v>-4.595171162835899</v>
       </c>
       <c r="G12">
-        <v>-4.409690846069566</v>
+        <v>-5.75907582896758</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-11.33065717013886</v>
       </c>
       <c r="E13">
-        <v>-15.06086433005378</v>
+        <v>-15.32773183179981</v>
       </c>
       <c r="F13">
-        <v>-4.794105251353006</v>
+        <v>-4.344749070030386</v>
       </c>
       <c r="G13">
-        <v>-4.886763632097319</v>
+        <v>-5.688157322425313</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-11.18791350688192</v>
       </c>
       <c r="E14">
-        <v>-15.93869995949267</v>
+        <v>-15.70931010863413</v>
       </c>
       <c r="F14">
-        <v>-4.458425100349159</v>
+        <v>-4.383398207942802</v>
       </c>
       <c r="G14">
-        <v>-4.624528698840569</v>
+        <v>-5.357447065234278</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-10.98370157190751</v>
       </c>
       <c r="E15">
-        <v>-17.66927894389393</v>
+        <v>-17.02992181264699</v>
       </c>
       <c r="F15">
-        <v>-4.160125856764044</v>
+        <v>-4.307584366503786</v>
       </c>
       <c r="G15">
-        <v>-3.84614330001051</v>
+        <v>-4.928112345882815</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-10.72859771692579</v>
       </c>
       <c r="E16">
-        <v>-17.41147744711127</v>
+        <v>-17.67400214228393</v>
       </c>
       <c r="F16">
-        <v>-3.904726932602511</v>
+        <v>-3.566857406553066</v>
       </c>
       <c r="G16">
-        <v>-4.095755123126018</v>
+        <v>-4.662368234354439</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-10.43781030205156</v>
       </c>
       <c r="E17">
-        <v>-19.63321925085847</v>
+        <v>-18.60837576970858</v>
       </c>
       <c r="F17">
-        <v>-3.907888810978997</v>
+        <v>-3.608831611220319</v>
       </c>
       <c r="G17">
-        <v>-3.734505083335207</v>
+        <v>-4.377883124528248</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-10.12829959942954</v>
       </c>
       <c r="E18">
-        <v>-20.30298508506692</v>
+        <v>-19.08594411008349</v>
       </c>
       <c r="F18">
-        <v>-3.596900635517798</v>
+        <v>-3.199922953441594</v>
       </c>
       <c r="G18">
-        <v>-3.729148620652666</v>
+        <v>-4.413600600351445</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-9.823432407751277</v>
       </c>
       <c r="E19">
-        <v>-20.22935662617621</v>
+        <v>-19.80926820638066</v>
       </c>
       <c r="F19">
-        <v>-3.264441176976036</v>
+        <v>-2.837614932274757</v>
       </c>
       <c r="G19">
-        <v>-3.799395086450462</v>
+        <v>-3.944125516336319</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-9.547250701831203</v>
       </c>
       <c r="E20">
-        <v>-20.63879860357972</v>
+        <v>-21.0034086883073</v>
       </c>
       <c r="F20">
-        <v>-2.996024459079509</v>
+        <v>-2.330948980556856</v>
       </c>
       <c r="G20">
-        <v>-3.442402408223153</v>
+        <v>-4.805916799482777</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-9.321990814807346</v>
       </c>
       <c r="E21">
-        <v>-21.76322322815828</v>
+        <v>-21.57542288258619</v>
       </c>
       <c r="F21">
-        <v>-2.584142790692136</v>
+        <v>-2.329111661657447</v>
       </c>
       <c r="G21">
-        <v>-3.069909755780977</v>
+        <v>-4.238280729682721</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-9.17044502376163</v>
       </c>
       <c r="E22">
-        <v>-22.68926899188282</v>
+        <v>-21.40912373160251</v>
       </c>
       <c r="F22">
-        <v>-2.561518420186876</v>
+        <v>-2.079499712171872</v>
       </c>
       <c r="G22">
-        <v>-4.088574549851339</v>
+        <v>-4.536878695142826</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-9.100518873194957</v>
       </c>
       <c r="E23">
-        <v>-23.01425492904329</v>
+        <v>-22.7754503807228</v>
       </c>
       <c r="F23">
-        <v>-2.4046405447099</v>
+        <v>-1.608832951044832</v>
       </c>
       <c r="G23">
-        <v>-3.444087475902642</v>
+        <v>-4.717151141938299</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-9.105696900527645</v>
       </c>
       <c r="E24">
-        <v>-23.85934969140671</v>
+        <v>-22.92935056987347</v>
       </c>
       <c r="F24">
-        <v>-2.054709989275694</v>
+        <v>-1.461169006189195</v>
       </c>
       <c r="G24">
-        <v>-3.650182177904431</v>
+        <v>-3.737971224514824</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-9.169069767148196</v>
       </c>
       <c r="E25">
-        <v>-22.3488953000443</v>
+        <v>-23.53442715288236</v>
       </c>
       <c r="F25">
-        <v>-1.783384873427938</v>
+        <v>-1.529052886481212</v>
       </c>
       <c r="G25">
-        <v>-4.106835519045958</v>
+        <v>-4.444570753871327</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-9.258225259993193</v>
       </c>
       <c r="E26">
-        <v>-24.29678216665164</v>
+        <v>-23.68436039880232</v>
       </c>
       <c r="F26">
-        <v>-1.387824527977924</v>
+        <v>-1.202269401383432</v>
       </c>
       <c r="G26">
-        <v>-3.941659159909562</v>
+        <v>-4.568755938140468</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-9.336437850648592</v>
       </c>
       <c r="E27">
-        <v>-23.54276407353048</v>
+        <v>-22.72479034199899</v>
       </c>
       <c r="F27">
-        <v>-1.615266052294973</v>
+        <v>-1.121577304309329</v>
       </c>
       <c r="G27">
-        <v>-4.833056651813722</v>
+        <v>-4.563594797644744</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-9.369123680898776</v>
       </c>
       <c r="E28">
-        <v>-23.97471709522612</v>
+        <v>-23.07993591605054</v>
       </c>
       <c r="F28">
-        <v>-1.704458855656604</v>
+        <v>-1.238838508747419</v>
       </c>
       <c r="G28">
-        <v>-4.314032632712324</v>
+        <v>-4.93549817298093</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-9.319063477138929</v>
       </c>
       <c r="E29">
-        <v>-23.69080441731523</v>
+        <v>-23.02035025505761</v>
       </c>
       <c r="F29">
-        <v>-1.624832039062502</v>
+        <v>-1.21035592396956</v>
       </c>
       <c r="G29">
-        <v>-4.105531164103486</v>
+        <v>-4.932565029633135</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-9.156998164831379</v>
       </c>
       <c r="E30">
-        <v>-23.55229198284262</v>
+        <v>-22.53353024228503</v>
       </c>
       <c r="F30">
-        <v>-1.767586250321746</v>
+        <v>-1.250906993438805</v>
       </c>
       <c r="G30">
-        <v>-5.0099490316136</v>
+        <v>-5.152113788706522</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-8.865338416477174</v>
       </c>
       <c r="E31">
-        <v>-23.49458111008887</v>
+        <v>-22.2048400133863</v>
       </c>
       <c r="F31">
-        <v>-1.736312895763856</v>
+        <v>-1.41142720038589</v>
       </c>
       <c r="G31">
-        <v>-4.648033572169394</v>
+        <v>-4.592641524206309</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-8.433555131603056</v>
       </c>
       <c r="E32">
-        <v>-22.43760810585456</v>
+        <v>-22.26910811650315</v>
       </c>
       <c r="F32">
-        <v>-1.721654106203916</v>
+        <v>-1.427012933069563</v>
       </c>
       <c r="G32">
-        <v>-3.660501148350339</v>
+        <v>-4.86027595723761</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.86977272375798</v>
       </c>
       <c r="E33">
-        <v>-22.61332648277419</v>
+        <v>-22.75146305390417</v>
       </c>
       <c r="F33">
-        <v>-1.707006913787615</v>
+        <v>-1.514542374686373</v>
       </c>
       <c r="G33">
-        <v>-4.445626817898354</v>
+        <v>-5.236463178501612</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-7.191306966824918</v>
       </c>
       <c r="E34">
-        <v>-22.25381998825326</v>
+        <v>-21.38601492874136</v>
       </c>
       <c r="F34">
-        <v>-1.841577683474603</v>
+        <v>-1.629566987136904</v>
       </c>
       <c r="G34">
-        <v>-4.480073044234471</v>
+        <v>-4.603864273584438</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.420362185493736</v>
       </c>
       <c r="E35">
-        <v>-22.7664206035515</v>
+        <v>-20.80766992779976</v>
       </c>
       <c r="F35">
-        <v>-1.782986428707192</v>
+        <v>-1.577066717882277</v>
       </c>
       <c r="G35">
-        <v>-3.800845105396662</v>
+        <v>-4.995551469063309</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.592624244419333</v>
       </c>
       <c r="E36">
-        <v>-19.99288877044368</v>
+        <v>-21.04699525063113</v>
       </c>
       <c r="F36">
-        <v>-2.071613654497221</v>
+        <v>-1.634524766042659</v>
       </c>
       <c r="G36">
-        <v>-4.343430277101053</v>
+        <v>-4.29896965050864</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.742527347442629</v>
       </c>
       <c r="E37">
-        <v>-20.98478307471375</v>
+        <v>-20.26534893758917</v>
       </c>
       <c r="F37">
-        <v>-2.137502826083296</v>
+        <v>-1.459188379729101</v>
       </c>
       <c r="G37">
-        <v>-3.912354210795934</v>
+        <v>-4.003801410227222</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.905405257994703</v>
       </c>
       <c r="E38">
-        <v>-20.22113744585229</v>
+        <v>-20.43208282207759</v>
       </c>
       <c r="F38">
-        <v>-1.983472877737145</v>
+        <v>-1.842771360902038</v>
       </c>
       <c r="G38">
-        <v>-3.014683235094855</v>
+        <v>-4.295864358792804</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.120918843152323</v>
       </c>
       <c r="E39">
-        <v>-20.43608146462636</v>
+        <v>-19.78223321655487</v>
       </c>
       <c r="F39">
-        <v>-1.663634424944436</v>
+        <v>-1.792155627488779</v>
       </c>
       <c r="G39">
-        <v>-3.947916090978785</v>
+        <v>-3.616626488318378</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.417851826316391</v>
       </c>
       <c r="E40">
-        <v>-20.44801399363657</v>
+        <v>-19.68805001414334</v>
       </c>
       <c r="F40">
-        <v>-1.849212745826206</v>
+        <v>-2.312714957286433</v>
       </c>
       <c r="G40">
-        <v>-2.993697686921415</v>
+        <v>-3.692533986988327</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-1.821090583472955</v>
       </c>
       <c r="E41">
-        <v>-19.62754507292686</v>
+        <v>-18.86255901575912</v>
       </c>
       <c r="F41">
-        <v>-1.881736106794921</v>
+        <v>-1.983332883646072</v>
       </c>
       <c r="G41">
-        <v>-3.481744931411852</v>
+        <v>-3.25817717005379</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-1.346227114795886</v>
       </c>
       <c r="E42">
-        <v>-18.86790714356218</v>
+        <v>-17.9620900732299</v>
       </c>
       <c r="F42">
-        <v>-1.730795968861212</v>
+        <v>-1.993578131683896</v>
       </c>
       <c r="G42">
-        <v>-3.00325854243883</v>
+        <v>-3.638985912890615</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-0.9941377979506267</v>
       </c>
       <c r="E43">
-        <v>-17.80883745586232</v>
+        <v>-18.20004779691095</v>
       </c>
       <c r="F43">
-        <v>-2.559476494538975</v>
+        <v>-2.044721535132737</v>
       </c>
       <c r="G43">
-        <v>-2.688948727849345</v>
+        <v>-3.164654258569379</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-0.7657826792659641</v>
       </c>
       <c r="E44">
-        <v>-17.70537541020907</v>
+        <v>-16.27762001117473</v>
       </c>
       <c r="F44">
-        <v>-2.166547872327655</v>
+        <v>-2.07507540187352</v>
       </c>
       <c r="G44">
-        <v>-2.817050287491444</v>
+        <v>-2.777105245014598</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.65130684982372</v>
       </c>
       <c r="E45">
-        <v>-17.19265705458663</v>
+        <v>-16.75293317149382</v>
       </c>
       <c r="F45">
-        <v>-2.105653756180461</v>
+        <v>-2.064472299117686</v>
       </c>
       <c r="G45">
-        <v>-2.97782031051507</v>
+        <v>-2.894798449481228</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.6356698658200144</v>
       </c>
       <c r="E46">
-        <v>-17.20054112783398</v>
+        <v>-16.29438895042514</v>
       </c>
       <c r="F46">
-        <v>-2.297594767083134</v>
+        <v>-2.136458254788366</v>
       </c>
       <c r="G46">
-        <v>-2.975112284263946</v>
+        <v>-2.490345790402927</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.7039515553471866</v>
       </c>
       <c r="E47">
-        <v>-17.16263780038978</v>
+        <v>-15.57369589752642</v>
       </c>
       <c r="F47">
-        <v>-2.143263293002364</v>
+        <v>-2.320147069624351</v>
       </c>
       <c r="G47">
-        <v>-2.173586172114382</v>
+        <v>-2.389735000918936</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.8367010429264645</v>
       </c>
       <c r="E48">
-        <v>-15.61954216838008</v>
+        <v>-15.1639550408384</v>
       </c>
       <c r="F48">
-        <v>-2.469753536039553</v>
+        <v>-2.318517670943044</v>
       </c>
       <c r="G48">
-        <v>-2.460531017276251</v>
+        <v>-2.568180026576732</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.017662061372075</v>
       </c>
       <c r="E49">
-        <v>-14.41364123945551</v>
+        <v>-15.06315573790167</v>
       </c>
       <c r="F49">
-        <v>-2.350315382066906</v>
+        <v>-2.270846783646738</v>
       </c>
       <c r="G49">
-        <v>-2.3997129851743</v>
+        <v>-2.472763483043858</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-1.232271795574139</v>
       </c>
       <c r="E50">
-        <v>-14.41935617365319</v>
+        <v>-13.76522263171922</v>
       </c>
       <c r="F50">
-        <v>-2.289546349397534</v>
+        <v>-2.809561441811549</v>
       </c>
       <c r="G50">
-        <v>-2.657243633219745</v>
+        <v>-2.447960875863638</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-1.469478157614804</v>
       </c>
       <c r="E51">
-        <v>-14.44666287191945</v>
+        <v>-13.96154103689974</v>
       </c>
       <c r="F51">
-        <v>-2.286552629603817</v>
+        <v>-2.595522902071796</v>
       </c>
       <c r="G51">
-        <v>-3.194485584423752</v>
+        <v>-1.912311297064021</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-1.722567678040447</v>
       </c>
       <c r="E52">
-        <v>-14.4586225717737</v>
+        <v>-13.11655948638651</v>
       </c>
       <c r="F52">
-        <v>-2.823690076233697</v>
+        <v>-2.60638942566172</v>
       </c>
       <c r="G52">
-        <v>-3.024704256442229</v>
+        <v>-2.160185083771412</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-1.984516279461347</v>
       </c>
       <c r="E53">
-        <v>-14.44194420200345</v>
+        <v>-12.93215096784616</v>
       </c>
       <c r="F53">
-        <v>-2.980221694136303</v>
+        <v>-2.476501416902757</v>
       </c>
       <c r="G53">
-        <v>-1.761171651014134</v>
+        <v>-2.382465042914697</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.255808613908094</v>
       </c>
       <c r="E54">
-        <v>-13.14667383853752</v>
+        <v>-12.00442514026477</v>
       </c>
       <c r="F54">
-        <v>-2.587071897828435</v>
+        <v>-2.821455969348347</v>
       </c>
       <c r="G54">
-        <v>-2.004470263786252</v>
+        <v>-1.885826932749851</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-2.537651820959274</v>
       </c>
       <c r="E55">
-        <v>-13.09928335804725</v>
+        <v>-11.89928755922869</v>
       </c>
       <c r="F55">
-        <v>-2.721084347885936</v>
+        <v>-2.593096613948996</v>
       </c>
       <c r="G55">
-        <v>-2.331380014698203</v>
+        <v>-1.949260295827827</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-2.832702014655854</v>
       </c>
       <c r="E56">
-        <v>-12.04915287803853</v>
+        <v>-11.53791080494258</v>
       </c>
       <c r="F56">
-        <v>-2.660377442771775</v>
+        <v>-2.799128154373289</v>
       </c>
       <c r="G56">
-        <v>-1.817454235727284</v>
+        <v>-1.825174427924864</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.147512685247489</v>
       </c>
       <c r="E57">
-        <v>-12.06764716588585</v>
+        <v>-11.69546547261745</v>
       </c>
       <c r="F57">
-        <v>-2.896626169315388</v>
+        <v>-2.987969414454687</v>
       </c>
       <c r="G57">
-        <v>-2.883251266640249</v>
+        <v>-2.127516620389884</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.482905644025183</v>
       </c>
       <c r="E58">
-        <v>-11.31277319117724</v>
+        <v>-10.47133290733801</v>
       </c>
       <c r="F58">
-        <v>-2.695142365932464</v>
+        <v>-2.888890046140644</v>
       </c>
       <c r="G58">
-        <v>-3.050106072365057</v>
+        <v>-2.114218158958631</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-3.83985769640272</v>
       </c>
       <c r="E59">
-        <v>-12.19780456581432</v>
+        <v>-10.74609806775341</v>
       </c>
       <c r="F59">
-        <v>-2.989911936014252</v>
+        <v>-2.898530585974424</v>
       </c>
       <c r="G59">
-        <v>-2.618410934044094</v>
+        <v>-2.221503008249793</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.217116927276042</v>
       </c>
       <c r="E60">
-        <v>-10.32849578018807</v>
+        <v>-10.37823201021431</v>
       </c>
       <c r="F60">
-        <v>-2.935079812520744</v>
+        <v>-2.853580885596315</v>
       </c>
       <c r="G60">
-        <v>-2.585136640828879</v>
+        <v>-2.120839250037174</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.606640317973337</v>
       </c>
       <c r="E61">
-        <v>-11.28093349042931</v>
+        <v>-9.540957922462132</v>
       </c>
       <c r="F61">
-        <v>-3.432230307882687</v>
+        <v>-2.810507437385546</v>
       </c>
       <c r="G61">
-        <v>-2.883896823020407</v>
+        <v>-2.340987217853169</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.004596074000377</v>
       </c>
       <c r="E62">
-        <v>-10.04936064235527</v>
+        <v>-8.954592994052943</v>
       </c>
       <c r="F62">
-        <v>-2.608159646801502</v>
+        <v>-2.711431382541114</v>
       </c>
       <c r="G62">
-        <v>-2.592452946470669</v>
+        <v>-2.255359957479919</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.404996741404453</v>
       </c>
       <c r="E63">
-        <v>-10.35300840999159</v>
+        <v>-9.308656262816658</v>
       </c>
       <c r="F63">
-        <v>-2.737171242848303</v>
+        <v>-2.87101967616005</v>
       </c>
       <c r="G63">
-        <v>-3.46626482047022</v>
+        <v>-2.581372550550728</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.797611993035781</v>
       </c>
       <c r="E64">
-        <v>-10.42129326955325</v>
+        <v>-8.694169510819837</v>
       </c>
       <c r="F64">
-        <v>-2.802641260528562</v>
+        <v>-2.968124216585819</v>
       </c>
       <c r="G64">
-        <v>-2.568511081130659</v>
+        <v>-2.50037012229584</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.176554520824727</v>
       </c>
       <c r="E65">
-        <v>-9.223443967414326</v>
+        <v>-9.756499699805218</v>
       </c>
       <c r="F65">
-        <v>-3.0135684523034</v>
+        <v>-2.962951062155336</v>
       </c>
       <c r="G65">
-        <v>-3.514823902440249</v>
+        <v>-2.520316159169949</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.529772381038486</v>
       </c>
       <c r="E66">
-        <v>-10.7444995164287</v>
+        <v>-9.220169880706779</v>
       </c>
       <c r="F66">
-        <v>-3.301338317831532</v>
+        <v>-2.65453496747983</v>
       </c>
       <c r="G66">
-        <v>-3.043283038008619</v>
+        <v>-2.371947439736433</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-6.84459357742322</v>
       </c>
       <c r="E67">
-        <v>-9.870861782394925</v>
+        <v>-8.156336238350852</v>
       </c>
       <c r="F67">
-        <v>-2.749354042241275</v>
+        <v>-3.034439997384336</v>
       </c>
       <c r="G67">
-        <v>-3.413941648222039</v>
+        <v>-2.138696332676003</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.110404867012055</v>
       </c>
       <c r="E68">
-        <v>-9.450750720229339</v>
+        <v>-8.929559589738542</v>
       </c>
       <c r="F68">
-        <v>-3.143701657813591</v>
+        <v>-3.01685872762732</v>
       </c>
       <c r="G68">
-        <v>-2.923884902589264</v>
+        <v>-2.000653204779473</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.314238545559779</v>
       </c>
       <c r="E69">
-        <v>-10.26430918960335</v>
+        <v>-8.310204728183475</v>
       </c>
       <c r="F69">
-        <v>-3.204696834783927</v>
+        <v>-3.36209741009207</v>
       </c>
       <c r="G69">
-        <v>-3.178343364374265</v>
+        <v>-2.007873504600623</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.443564077543838</v>
       </c>
       <c r="E70">
-        <v>-8.998261068908908</v>
+        <v>-8.818068559669697</v>
       </c>
       <c r="F70">
-        <v>-3.20612991039077</v>
+        <v>-3.122502907608549</v>
       </c>
       <c r="G70">
-        <v>-3.439164694685746</v>
+        <v>-2.127341161476302</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.487364355286577</v>
       </c>
       <c r="E71">
-        <v>-10.03217961197017</v>
+        <v>-8.424824933791619</v>
       </c>
       <c r="F71">
-        <v>-3.045382730775318</v>
+        <v>-3.270896644146053</v>
       </c>
       <c r="G71">
-        <v>-2.821181848324454</v>
+        <v>-2.249622782060362</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-7.437475622554484</v>
       </c>
       <c r="E72">
-        <v>-10.24798856927971</v>
+        <v>-7.964079874355207</v>
       </c>
       <c r="F72">
-        <v>-3.248415581201477</v>
+        <v>-3.427515240625952</v>
       </c>
       <c r="G72">
-        <v>-3.044120606030055</v>
+        <v>-2.272975370294381</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-7.289418433028318</v>
       </c>
       <c r="E73">
-        <v>-10.43060381211302</v>
+        <v>-8.458503194986664</v>
       </c>
       <c r="F73">
-        <v>-3.240408581886017</v>
+        <v>-3.420467490762934</v>
       </c>
       <c r="G73">
-        <v>-3.447566859264416</v>
+        <v>-2.754514082254611</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-7.045390420448424</v>
       </c>
       <c r="E74">
-        <v>-10.92684305082155</v>
+        <v>-8.809324076360886</v>
       </c>
       <c r="F74">
-        <v>-3.277866527473207</v>
+        <v>-3.353373044605785</v>
       </c>
       <c r="G74">
-        <v>-2.031116844831846</v>
+        <v>-1.908325400234739</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-6.710816088520928</v>
       </c>
       <c r="E75">
-        <v>-11.08213800996659</v>
+        <v>-8.804827301671271</v>
       </c>
       <c r="F75">
-        <v>-3.267500337794575</v>
+        <v>-3.471624976457623</v>
       </c>
       <c r="G75">
-        <v>-1.723368531501196</v>
+        <v>-1.00997245215257</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-6.296510767609911</v>
       </c>
       <c r="E76">
-        <v>-9.874570602607207</v>
+        <v>-8.954792246909282</v>
       </c>
       <c r="F76">
-        <v>-3.741482225267618</v>
+        <v>-3.672893404315819</v>
       </c>
       <c r="G76">
-        <v>-2.50627944608344</v>
+        <v>-0.6661822295358749</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.821947421902774</v>
       </c>
       <c r="E77">
-        <v>-10.17714965037772</v>
+        <v>-9.517446085414308</v>
       </c>
       <c r="F77">
-        <v>-3.501206804778996</v>
+        <v>-3.788786974171887</v>
       </c>
       <c r="G77">
-        <v>-0.9906686611130796</v>
+        <v>-0.7753342265111852</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.308065233099822</v>
       </c>
       <c r="E78">
-        <v>-10.76132279736719</v>
+        <v>-9.813132795745144</v>
       </c>
       <c r="F78">
-        <v>-3.658637201313639</v>
+        <v>-3.825758668093634</v>
       </c>
       <c r="G78">
-        <v>-1.394783644546374</v>
+        <v>-0.8004579566087142</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.780654456253159</v>
       </c>
       <c r="E79">
-        <v>-13.1275953775432</v>
+        <v>-10.23558055049869</v>
       </c>
       <c r="F79">
-        <v>-4.241063150589374</v>
+        <v>-3.949629416038661</v>
       </c>
       <c r="G79">
-        <v>-1.238108766354826</v>
+        <v>0.3630531364413801</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.269628995574011</v>
       </c>
       <c r="E80">
-        <v>-11.36548010015252</v>
+        <v>-10.43644554358291</v>
       </c>
       <c r="F80">
-        <v>-3.929316190587211</v>
+        <v>-4.263592258843313</v>
       </c>
       <c r="G80">
-        <v>-2.161575512897906</v>
+        <v>0.1369461866546973</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.802688036909244</v>
       </c>
       <c r="E81">
-        <v>-12.26375726126203</v>
+        <v>-11.06414638273412</v>
       </c>
       <c r="F81">
-        <v>-4.369215729639472</v>
+        <v>-4.24026874625009</v>
       </c>
       <c r="G81">
-        <v>-0.8190897069037325</v>
+        <v>0.2647100706517902</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.40925696324507</v>
       </c>
       <c r="E82">
-        <v>-14.23243888051259</v>
+        <v>-11.98161068821413</v>
       </c>
       <c r="F82">
-        <v>-4.200695150316149</v>
+        <v>-4.520313257379713</v>
       </c>
       <c r="G82">
-        <v>-1.185245975183744</v>
+        <v>0.5842207522834703</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.111675241197702</v>
       </c>
       <c r="E83">
-        <v>-13.73302970999869</v>
+        <v>-12.97821007697817</v>
       </c>
       <c r="F83">
-        <v>-4.216725716295125</v>
+        <v>-4.691378581364436</v>
       </c>
       <c r="G83">
-        <v>-0.5319991977381351</v>
+        <v>0.9971550290333833</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.925418542784897</v>
       </c>
       <c r="E84">
-        <v>-14.05403511850641</v>
+        <v>-14.38786063692985</v>
       </c>
       <c r="F84">
-        <v>-4.531813482032779</v>
+        <v>-4.826675000896277</v>
       </c>
       <c r="G84">
-        <v>-0.2153256536336105</v>
+        <v>1.253149583948606</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.862248364121092</v>
       </c>
       <c r="E85">
-        <v>-15.63912328998924</v>
+        <v>-14.63017475260628</v>
       </c>
       <c r="F85">
-        <v>-4.86877925924577</v>
+        <v>-5.017094300880007</v>
       </c>
       <c r="G85">
-        <v>0.5140835344884709</v>
+        <v>1.310551133054029</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.921684369364151</v>
       </c>
       <c r="E86">
-        <v>-16.67483058028353</v>
+        <v>-15.42395737598879</v>
       </c>
       <c r="F86">
-        <v>-4.864193417303872</v>
+        <v>-5.358891945153529</v>
       </c>
       <c r="G86">
-        <v>0.2277577613424452</v>
+        <v>1.750466355949003</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.101998809207938</v>
       </c>
       <c r="E87">
-        <v>-18.20622916393142</v>
+        <v>-16.97852363265993</v>
       </c>
       <c r="F87">
-        <v>-4.907406031238311</v>
+        <v>-5.400661543072291</v>
       </c>
       <c r="G87">
-        <v>0.4422910439238359</v>
+        <v>1.7615599940511</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.396162832983666</v>
       </c>
       <c r="E88">
-        <v>-19.02986801644651</v>
+        <v>-18.44720737977559</v>
       </c>
       <c r="F88">
-        <v>-5.277426981292614</v>
+        <v>-5.758935414987493</v>
       </c>
       <c r="G88">
-        <v>0.5845220119275439</v>
+        <v>1.678826150479174</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.794583588118279</v>
       </c>
       <c r="E89">
-        <v>-20.56833101954637</v>
+        <v>-19.90507713096094</v>
       </c>
       <c r="F89">
-        <v>-5.612958026163956</v>
+        <v>-5.707683495408885</v>
       </c>
       <c r="G89">
-        <v>-0.09084252026593528</v>
+        <v>1.910104172398198</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.288305259688623</v>
       </c>
       <c r="E90">
-        <v>-22.75162155049444</v>
+        <v>-20.68679137111301</v>
       </c>
       <c r="F90">
-        <v>-5.738903834452996</v>
+        <v>-5.969235532638413</v>
       </c>
       <c r="G90">
-        <v>-0.1056108639166241</v>
+        <v>2.26699422371379</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.861086626090752</v>
       </c>
       <c r="E91">
-        <v>-24.91468338805024</v>
+        <v>-22.54637752304479</v>
       </c>
       <c r="F91">
-        <v>-5.497369295512119</v>
+        <v>-6.143870291761798</v>
       </c>
       <c r="G91">
-        <v>0.1201484785884353</v>
+        <v>1.409420575584363</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.499067729003555</v>
       </c>
       <c r="E92">
-        <v>-26.57594049234209</v>
+        <v>-25.26445366345469</v>
       </c>
       <c r="F92">
-        <v>-5.770214465544012</v>
+        <v>-6.489858646726082</v>
       </c>
       <c r="G92">
-        <v>-0.0150310274166251</v>
+        <v>1.559279040510552</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.185156352970709</v>
       </c>
       <c r="E93">
-        <v>-28.01298832004017</v>
+        <v>-26.82740212551402</v>
       </c>
       <c r="F93">
-        <v>-5.780149904173189</v>
+        <v>-6.417483358376087</v>
       </c>
       <c r="G93">
-        <v>-0.7820612550469842</v>
+        <v>1.035835443114228</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.893425275634868</v>
       </c>
       <c r="E94">
-        <v>-30.56298109070737</v>
+        <v>-29.05825069049065</v>
       </c>
       <c r="F94">
-        <v>-5.904216146825276</v>
+        <v>-6.940399393434705</v>
       </c>
       <c r="G94">
-        <v>-1.069817183865975</v>
+        <v>1.356090997492244</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-7.605419930258424</v>
       </c>
       <c r="E95">
-        <v>-32.18869420251301</v>
+        <v>-31.57628602008571</v>
       </c>
       <c r="F95">
-        <v>-6.150358065260524</v>
+        <v>-6.98071686329636</v>
       </c>
       <c r="G95">
-        <v>-1.366508275095459</v>
+        <v>0.2686794147533764</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-8.294459187580756</v>
       </c>
       <c r="E96">
-        <v>-33.78935806034522</v>
+        <v>-33.41823829423162</v>
       </c>
       <c r="F96">
-        <v>-6.116642683599181</v>
+        <v>-6.959888393320369</v>
       </c>
       <c r="G96">
-        <v>-1.961890027060146</v>
+        <v>0.03474302476631719</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-8.934699107010108</v>
       </c>
       <c r="E97">
-        <v>-36.8745236250019</v>
+        <v>-36.21435362721569</v>
       </c>
       <c r="F97">
-        <v>-6.420018162628653</v>
+        <v>-7.333417479325528</v>
       </c>
       <c r="G97">
-        <v>-1.824042221350433</v>
+        <v>-0.1276723393903272</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-9.503755017807878</v>
       </c>
       <c r="E98">
-        <v>-39.72704563022552</v>
+        <v>-37.90457485126061</v>
       </c>
       <c r="F98">
-        <v>-6.505258410927826</v>
+        <v>-7.25310560288931</v>
       </c>
       <c r="G98">
-        <v>-3.458206952627634</v>
+        <v>-0.9719773209983544</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-9.978510864612538</v>
       </c>
       <c r="E99">
-        <v>-41.96055693791865</v>
+        <v>-41.30448068063539</v>
       </c>
       <c r="F99">
-        <v>-6.950626417389667</v>
+        <v>-7.591141630786718</v>
       </c>
       <c r="G99">
-        <v>-2.468628611665308</v>
+        <v>-2.027021699999767</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-10.33869668262864</v>
       </c>
       <c r="E100">
-        <v>-44.61598390466943</v>
+        <v>-43.62828523156746</v>
       </c>
       <c r="F100">
-        <v>-6.76659341589782</v>
+        <v>-7.487461924101228</v>
       </c>
       <c r="G100">
-        <v>-3.724762147813132</v>
+        <v>-2.849152647585756</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-10.5771706967368</v>
       </c>
       <c r="E101">
-        <v>-46.46243068926795</v>
+        <v>-46.36691611549817</v>
       </c>
       <c r="F101">
-        <v>-7.008629531301092</v>
+        <v>-7.835830592797456</v>
       </c>
       <c r="G101">
-        <v>-4.713453262570932</v>
+        <v>-3.093166338194357</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-10.67528617166873</v>
       </c>
       <c r="E102">
-        <v>-49.60920840703599</v>
+        <v>-48.27060734002765</v>
       </c>
       <c r="F102">
-        <v>-7.062874756489716</v>
+        <v>-7.884104945746701</v>
       </c>
       <c r="G102">
-        <v>-5.363627853756097</v>
+        <v>-4.19408825727899</v>
       </c>
     </row>
   </sheetData>
